--- a/mmkBelgeler/KU013 Aylık Satış Planı.xlsx
+++ b/mmkBelgeler/KU013 Aylık Satış Planı.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\myilmaz\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/begumyilmaz/Documents/okul/koç/4.2/bitirme/bitirmeRepoYeni/indr491/mmkBelgeler/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C59F6B-EB1C-CB47-9A09-26D667D05FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26760" windowHeight="12390"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="26760" windowHeight="12400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,9 +72,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
@@ -103,12 +104,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -122,9 +141,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -136,6 +155,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -416,20 +441,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -452,215 +477,221 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2025</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B2" s="7">
+        <v>3</v>
+      </c>
+      <c r="C2" s="7">
         <v>3100</v>
       </c>
-      <c r="D2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="8">
         <v>5500</v>
       </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2025</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
+      <c r="G2" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B3" s="7">
+        <v>3</v>
+      </c>
+      <c r="C3" s="7">
         <v>3100</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4">
+      <c r="E3" s="7"/>
+      <c r="F3" s="8">
         <v>7700</v>
       </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2025</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
+      <c r="G3" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B4" s="5">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5">
         <v>3100</v>
       </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6">
         <v>1000</v>
       </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2025</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="9">
+        <v>3</v>
+      </c>
+      <c r="C5" s="9">
         <v>3100</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="10">
         <v>500</v>
       </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2025</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
+      <c r="G5" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="9">
+        <v>3</v>
+      </c>
+      <c r="C6" s="9">
         <v>3100</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="4">
+      <c r="E6" s="9"/>
+      <c r="F6" s="10">
         <v>8300</v>
       </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2025</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
+      <c r="G6" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7">
         <v>4100</v>
       </c>
-      <c r="D7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="8">
         <v>4475</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2025</v>
-      </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="C8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="7">
+        <v>3</v>
+      </c>
+      <c r="C8" s="7">
         <v>4100</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="4">
+      <c r="E8" s="7"/>
+      <c r="F8" s="8">
         <v>8200</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="8">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2025</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-      <c r="C9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="5">
+        <v>3</v>
+      </c>
+      <c r="C9" s="5">
         <v>4100</v>
       </c>
-      <c r="D9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="D9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6">
         <v>1500</v>
       </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>2025</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="9">
+        <v>3</v>
+      </c>
+      <c r="C10" s="9">
         <v>4100</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="10">
         <v>500</v>
       </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>2025</v>
-      </c>
-      <c r="B11">
-        <v>3</v>
-      </c>
-      <c r="C11">
+      <c r="G10" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="9">
+        <v>3</v>
+      </c>
+      <c r="C11" s="9">
         <v>4100</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="4">
+      <c r="E11" s="9"/>
+      <c r="F11" s="10">
         <v>5025</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="10">
         <v>175</v>
       </c>
     </row>
